--- a/data/loto_pool.xlsx
+++ b/data/loto_pool.xlsx
@@ -9043,7 +9043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B232"/>
+  <dimension ref="A1:B233"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11822,6 +11822,18 @@
       <c r="B232" s="2" t="inlineStr">
         <is>
           <t>07, 08, 12, 13, 20</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-05  Sáb</t>
+        </is>
+      </c>
+      <c r="B233" s="2" t="inlineStr">
+        <is>
+          <t>07, 08, 12, 20, 27</t>
         </is>
       </c>
     </row>

--- a/data/loto_pool.xlsx
+++ b/data/loto_pool.xlsx
@@ -9043,7 +9043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B233"/>
+  <dimension ref="A1:B234"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11834,6 +11834,18 @@
       <c r="B233" s="2" t="inlineStr">
         <is>
           <t>07, 08, 12, 20, 27</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-06  Dom</t>
+        </is>
+      </c>
+      <c r="B234" s="2" t="inlineStr">
+        <is>
+          <t>06, 11, 13, 21, 27</t>
         </is>
       </c>
     </row>

--- a/data/loto_pool.xlsx
+++ b/data/loto_pool.xlsx
@@ -9043,7 +9043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B234"/>
+  <dimension ref="A1:B235"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11846,6 +11846,18 @@
       <c r="B234" s="2" t="inlineStr">
         <is>
           <t>06, 11, 13, 21, 27</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09  Mié</t>
+        </is>
+      </c>
+      <c r="B235" s="2" t="inlineStr">
+        <is>
+          <t>02, 06, 25, 28, 29</t>
         </is>
       </c>
     </row>

--- a/data/loto_pool.xlsx
+++ b/data/loto_pool.xlsx
@@ -9043,7 +9043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B235"/>
+  <dimension ref="A1:B236"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11858,6 +11858,18 @@
       <c r="B235" s="2" t="inlineStr">
         <is>
           <t>02, 06, 25, 28, 29</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-10  Jue</t>
+        </is>
+      </c>
+      <c r="B236" s="2" t="inlineStr">
+        <is>
+          <t>04, 05, 10, 11, 17</t>
         </is>
       </c>
     </row>

--- a/data/loto_pool.xlsx
+++ b/data/loto_pool.xlsx
@@ -9043,7 +9043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B236"/>
+  <dimension ref="A1:B237"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11870,6 +11870,18 @@
       <c r="B236" s="2" t="inlineStr">
         <is>
           <t>04, 05, 10, 11, 17</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11  Vie</t>
+        </is>
+      </c>
+      <c r="B237" s="2" t="inlineStr">
+        <is>
+          <t>01, 12, 17, 26, 29</t>
         </is>
       </c>
     </row>

--- a/data/loto_pool.xlsx
+++ b/data/loto_pool.xlsx
@@ -9043,7 +9043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B237"/>
+  <dimension ref="A1:B238"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11882,6 +11882,18 @@
       <c r="B237" s="2" t="inlineStr">
         <is>
           <t>01, 12, 17, 26, 29</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12  Sáb</t>
+        </is>
+      </c>
+      <c r="B238" s="2" t="inlineStr">
+        <is>
+          <t>01, 05, 17, 22, 26</t>
         </is>
       </c>
     </row>

--- a/data/loto_pool.xlsx
+++ b/data/loto_pool.xlsx
@@ -9043,7 +9043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B238"/>
+  <dimension ref="A1:B239"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11894,6 +11894,18 @@
       <c r="B238" s="2" t="inlineStr">
         <is>
           <t>01, 05, 17, 22, 26</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13  Dom</t>
+        </is>
+      </c>
+      <c r="B239" s="2" t="inlineStr">
+        <is>
+          <t>07, 23, 26, 28, 30</t>
         </is>
       </c>
     </row>

--- a/data/loto_pool.xlsx
+++ b/data/loto_pool.xlsx
@@ -9043,7 +9043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B239"/>
+  <dimension ref="A1:B240"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11906,6 +11906,18 @@
       <c r="B239" s="2" t="inlineStr">
         <is>
           <t>07, 23, 26, 28, 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14  Lun</t>
+        </is>
+      </c>
+      <c r="B240" s="2" t="inlineStr">
+        <is>
+          <t>04, 14, 17, 20, 25</t>
         </is>
       </c>
     </row>

--- a/data/loto_pool.xlsx
+++ b/data/loto_pool.xlsx
@@ -9043,7 +9043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B240"/>
+  <dimension ref="A1:B241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11918,6 +11918,18 @@
       <c r="B240" s="2" t="inlineStr">
         <is>
           <t>04, 14, 17, 20, 25</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15  Mar</t>
+        </is>
+      </c>
+      <c r="B241" s="2" t="inlineStr">
+        <is>
+          <t>05, 08, 18, 24, 28</t>
         </is>
       </c>
     </row>

--- a/data/loto_pool.xlsx
+++ b/data/loto_pool.xlsx
@@ -9043,7 +9043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B241"/>
+  <dimension ref="A1:B242"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11930,6 +11930,18 @@
       <c r="B241" s="2" t="inlineStr">
         <is>
           <t>05, 08, 18, 24, 28</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16  Mié</t>
+        </is>
+      </c>
+      <c r="B242" s="2" t="inlineStr">
+        <is>
+          <t>04, 15, 16, 17, 18</t>
         </is>
       </c>
     </row>

--- a/data/loto_pool.xlsx
+++ b/data/loto_pool.xlsx
@@ -9043,7 +9043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B242"/>
+  <dimension ref="A1:B243"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11942,6 +11942,18 @@
       <c r="B242" s="2" t="inlineStr">
         <is>
           <t>04, 15, 16, 17, 18</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17  Jue</t>
+        </is>
+      </c>
+      <c r="B243" s="2" t="inlineStr">
+        <is>
+          <t>03, 10, 11, 24, 30</t>
         </is>
       </c>
     </row>

--- a/data/loto_pool.xlsx
+++ b/data/loto_pool.xlsx
@@ -9043,7 +9043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B243"/>
+  <dimension ref="A1:B244"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11954,6 +11954,18 @@
       <c r="B243" s="2" t="inlineStr">
         <is>
           <t>03, 10, 11, 24, 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18  Vie</t>
+        </is>
+      </c>
+      <c r="B244" s="2" t="inlineStr">
+        <is>
+          <t>03, 05, 06, 16, 30</t>
         </is>
       </c>
     </row>

--- a/data/loto_pool.xlsx
+++ b/data/loto_pool.xlsx
@@ -9043,7 +9043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B244"/>
+  <dimension ref="A1:B245"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11966,6 +11966,18 @@
       <c r="B244" s="2" t="inlineStr">
         <is>
           <t>03, 05, 06, 16, 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19  Sáb</t>
+        </is>
+      </c>
+      <c r="B245" s="2" t="inlineStr">
+        <is>
+          <t>12, 13, 18, 24, 28</t>
         </is>
       </c>
     </row>

--- a/data/loto_pool.xlsx
+++ b/data/loto_pool.xlsx
@@ -9043,7 +9043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B245"/>
+  <dimension ref="A1:B246"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11978,6 +11978,18 @@
       <c r="B245" s="2" t="inlineStr">
         <is>
           <t>12, 13, 18, 24, 28</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-20  Dom</t>
+        </is>
+      </c>
+      <c r="B246" s="2" t="inlineStr">
+        <is>
+          <t>02, 04, 22, 23, 31</t>
         </is>
       </c>
     </row>

--- a/data/loto_pool.xlsx
+++ b/data/loto_pool.xlsx
@@ -9043,7 +9043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B246"/>
+  <dimension ref="A1:B247"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11990,6 +11990,18 @@
       <c r="B246" s="2" t="inlineStr">
         <is>
           <t>02, 04, 22, 23, 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21  Lun</t>
+        </is>
+      </c>
+      <c r="B247" s="2" t="inlineStr">
+        <is>
+          <t>15, 19, 21, 23, 29</t>
         </is>
       </c>
     </row>

--- a/data/loto_pool.xlsx
+++ b/data/loto_pool.xlsx
@@ -9043,7 +9043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B247"/>
+  <dimension ref="A1:B248"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12002,6 +12002,18 @@
       <c r="B247" s="2" t="inlineStr">
         <is>
           <t>15, 19, 21, 23, 29</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-22  Mar</t>
+        </is>
+      </c>
+      <c r="B248" s="2" t="inlineStr">
+        <is>
+          <t>12, 15, 23, 27, 31</t>
         </is>
       </c>
     </row>

--- a/data/loto_pool.xlsx
+++ b/data/loto_pool.xlsx
@@ -9043,7 +9043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B248"/>
+  <dimension ref="A1:B249"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12014,6 +12014,18 @@
       <c r="B248" s="2" t="inlineStr">
         <is>
           <t>12, 15, 23, 27, 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23  Mié</t>
+        </is>
+      </c>
+      <c r="B249" s="2" t="inlineStr">
+        <is>
+          <t>07, 08, 12, 16, 28</t>
         </is>
       </c>
     </row>

--- a/data/loto_pool.xlsx
+++ b/data/loto_pool.xlsx
@@ -9043,7 +9043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B249"/>
+  <dimension ref="A1:B250"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12026,6 +12026,18 @@
       <c r="B249" s="2" t="inlineStr">
         <is>
           <t>07, 08, 12, 16, 28</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-24  Jue</t>
+        </is>
+      </c>
+      <c r="B250" s="2" t="inlineStr">
+        <is>
+          <t>12, 20, 21, 24, 27</t>
         </is>
       </c>
     </row>

--- a/data/loto_pool.xlsx
+++ b/data/loto_pool.xlsx
@@ -9043,7 +9043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B250"/>
+  <dimension ref="A1:B251"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12038,6 +12038,18 @@
       <c r="B250" s="2" t="inlineStr">
         <is>
           <t>12, 20, 21, 24, 27</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-25  Vie</t>
+        </is>
+      </c>
+      <c r="B251" s="2" t="inlineStr">
+        <is>
+          <t>01, 04, 18, 26, 31</t>
         </is>
       </c>
     </row>

--- a/data/loto_pool.xlsx
+++ b/data/loto_pool.xlsx
@@ -9043,7 +9043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B251"/>
+  <dimension ref="A1:B252"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12050,6 +12050,18 @@
       <c r="B251" s="2" t="inlineStr">
         <is>
           <t>01, 04, 18, 26, 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-26  Sáb</t>
+        </is>
+      </c>
+      <c r="B252" s="2" t="inlineStr">
+        <is>
+          <t>14, 22, 25, 29, 30</t>
         </is>
       </c>
     </row>

--- a/data/loto_pool.xlsx
+++ b/data/loto_pool.xlsx
@@ -9043,7 +9043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B252"/>
+  <dimension ref="A1:B253"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12062,6 +12062,18 @@
       <c r="B252" s="2" t="inlineStr">
         <is>
           <t>14, 22, 25, 29, 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27  Dom</t>
+        </is>
+      </c>
+      <c r="B253" s="2" t="inlineStr">
+        <is>
+          <t>01, 15, 16, 27, 28</t>
         </is>
       </c>
     </row>

--- a/data/loto_pool.xlsx
+++ b/data/loto_pool.xlsx
@@ -9043,7 +9043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B253"/>
+  <dimension ref="A1:B254"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12074,6 +12074,18 @@
       <c r="B253" s="2" t="inlineStr">
         <is>
           <t>01, 15, 16, 27, 28</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28  Lun</t>
+        </is>
+      </c>
+      <c r="B254" s="2" t="inlineStr">
+        <is>
+          <t>06, 13, 17, 28, 29</t>
         </is>
       </c>
     </row>

--- a/data/loto_pool.xlsx
+++ b/data/loto_pool.xlsx
@@ -9043,7 +9043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B254"/>
+  <dimension ref="A1:B255"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12086,6 +12086,18 @@
       <c r="B254" s="2" t="inlineStr">
         <is>
           <t>06, 13, 17, 28, 29</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29  Mar</t>
+        </is>
+      </c>
+      <c r="B255" s="2" t="inlineStr">
+        <is>
+          <t>03, 08, 14, 24, 27</t>
         </is>
       </c>
     </row>

--- a/data/loto_pool.xlsx
+++ b/data/loto_pool.xlsx
@@ -9043,7 +9043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B255"/>
+  <dimension ref="A1:B257"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12098,6 +12098,30 @@
       <c r="B255" s="2" t="inlineStr">
         <is>
           <t>03, 08, 14, 24, 27</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30  Mié</t>
+        </is>
+      </c>
+      <c r="B256" s="2" t="inlineStr">
+        <is>
+          <t>01, 03, 05, 08, 25</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-01  Jue</t>
+        </is>
+      </c>
+      <c r="B257" s="2" t="inlineStr">
+        <is>
+          <t>03, 10, 22, 27, 31</t>
         </is>
       </c>
     </row>

--- a/data/loto_pool.xlsx
+++ b/data/loto_pool.xlsx
@@ -9043,7 +9043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B257"/>
+  <dimension ref="A1:B258"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12122,6 +12122,18 @@
       <c r="B257" s="2" t="inlineStr">
         <is>
           <t>03, 10, 22, 27, 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-02  Vie</t>
+        </is>
+      </c>
+      <c r="B258" s="2" t="inlineStr">
+        <is>
+          <t>04, 05, 06, 27, 31</t>
         </is>
       </c>
     </row>

--- a/data/loto_pool.xlsx
+++ b/data/loto_pool.xlsx
@@ -9043,7 +9043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B258"/>
+  <dimension ref="A1:B259"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12134,6 +12134,18 @@
       <c r="B258" s="2" t="inlineStr">
         <is>
           <t>04, 05, 06, 27, 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03  Sáb</t>
+        </is>
+      </c>
+      <c r="B259" s="2" t="inlineStr">
+        <is>
+          <t>03, 15, 21, 25, 30</t>
         </is>
       </c>
     </row>

--- a/data/loto_pool.xlsx
+++ b/data/loto_pool.xlsx
@@ -9043,7 +9043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B259"/>
+  <dimension ref="A1:B260"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12146,6 +12146,18 @@
       <c r="B259" s="2" t="inlineStr">
         <is>
           <t>03, 15, 21, 25, 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04  Dom</t>
+        </is>
+      </c>
+      <c r="B260" s="2" t="inlineStr">
+        <is>
+          <t>08, 19, 25, 27, 31</t>
         </is>
       </c>
     </row>

--- a/data/loto_pool.xlsx
+++ b/data/loto_pool.xlsx
@@ -9043,7 +9043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B260"/>
+  <dimension ref="A1:B261"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12158,6 +12158,18 @@
       <c r="B260" s="2" t="inlineStr">
         <is>
           <t>08, 19, 25, 27, 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05  Lun</t>
+        </is>
+      </c>
+      <c r="B261" s="2" t="inlineStr">
+        <is>
+          <t>05, 13, 19, 20, 29</t>
         </is>
       </c>
     </row>

--- a/data/loto_pool.xlsx
+++ b/data/loto_pool.xlsx
@@ -9043,7 +9043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B261"/>
+  <dimension ref="A1:B262"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12170,6 +12170,18 @@
       <c r="B261" s="2" t="inlineStr">
         <is>
           <t>05, 13, 19, 20, 29</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-06  Mar</t>
+        </is>
+      </c>
+      <c r="B262" s="2" t="inlineStr">
+        <is>
+          <t>02, 03, 15, 22, 24</t>
         </is>
       </c>
     </row>

--- a/data/loto_pool.xlsx
+++ b/data/loto_pool.xlsx
@@ -9043,7 +9043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B262"/>
+  <dimension ref="A1:B263"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12182,6 +12182,18 @@
       <c r="B262" s="2" t="inlineStr">
         <is>
           <t>02, 03, 15, 22, 24</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07  Mié</t>
+        </is>
+      </c>
+      <c r="B263" s="2" t="inlineStr">
+        <is>
+          <t>03, 04, 17, 18, 20</t>
         </is>
       </c>
     </row>

--- a/data/loto_pool.xlsx
+++ b/data/loto_pool.xlsx
@@ -9043,7 +9043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B263"/>
+  <dimension ref="A1:B264"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12194,6 +12194,18 @@
       <c r="B263" s="2" t="inlineStr">
         <is>
           <t>03, 04, 17, 18, 20</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08  Jue</t>
+        </is>
+      </c>
+      <c r="B264" s="2" t="inlineStr">
+        <is>
+          <t>03, 04, 17, 19, 28</t>
         </is>
       </c>
     </row>

--- a/data/loto_pool.xlsx
+++ b/data/loto_pool.xlsx
@@ -9043,7 +9043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B264"/>
+  <dimension ref="A1:B265"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12206,6 +12206,18 @@
       <c r="B264" s="2" t="inlineStr">
         <is>
           <t>03, 04, 17, 19, 28</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09  Vie</t>
+        </is>
+      </c>
+      <c r="B265" s="2" t="inlineStr">
+        <is>
+          <t>08, 10, 15, 18, 22</t>
         </is>
       </c>
     </row>

--- a/data/loto_pool.xlsx
+++ b/data/loto_pool.xlsx
@@ -9043,7 +9043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B265"/>
+  <dimension ref="A1:B266"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12218,6 +12218,18 @@
       <c r="B265" s="2" t="inlineStr">
         <is>
           <t>08, 10, 15, 18, 22</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-10  Sáb</t>
+        </is>
+      </c>
+      <c r="B266" s="2" t="inlineStr">
+        <is>
+          <t>03, 05, 13, 18, 30</t>
         </is>
       </c>
     </row>

--- a/data/loto_pool.xlsx
+++ b/data/loto_pool.xlsx
@@ -9043,7 +9043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B266"/>
+  <dimension ref="A1:B267"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12230,6 +12230,18 @@
       <c r="B266" s="2" t="inlineStr">
         <is>
           <t>03, 05, 13, 18, 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-11  Dom</t>
+        </is>
+      </c>
+      <c r="B267" s="2" t="inlineStr">
+        <is>
+          <t>11, 13, 15, 18, 26</t>
         </is>
       </c>
     </row>

--- a/data/loto_pool.xlsx
+++ b/data/loto_pool.xlsx
@@ -9043,7 +9043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B267"/>
+  <dimension ref="A1:B268"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12242,6 +12242,18 @@
       <c r="B267" s="2" t="inlineStr">
         <is>
           <t>11, 13, 15, 18, 26</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12  Lun</t>
+        </is>
+      </c>
+      <c r="B268" s="2" t="inlineStr">
+        <is>
+          <t>05, 14, 23, 24, 26</t>
         </is>
       </c>
     </row>

--- a/data/loto_pool.xlsx
+++ b/data/loto_pool.xlsx
@@ -9043,7 +9043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B268"/>
+  <dimension ref="A1:B269"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12254,6 +12254,18 @@
       <c r="B268" s="2" t="inlineStr">
         <is>
           <t>05, 14, 23, 24, 26</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13  Mar</t>
+        </is>
+      </c>
+      <c r="B269" s="2" t="inlineStr">
+        <is>
+          <t>07, 10, 15, 17, 21</t>
         </is>
       </c>
     </row>

--- a/data/loto_pool.xlsx
+++ b/data/loto_pool.xlsx
@@ -9043,7 +9043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B269"/>
+  <dimension ref="A1:B270"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12266,6 +12266,18 @@
       <c r="B269" s="2" t="inlineStr">
         <is>
           <t>07, 10, 15, 17, 21</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14  Mié</t>
+        </is>
+      </c>
+      <c r="B270" s="2" t="inlineStr">
+        <is>
+          <t>01, 16, 20, 24, 27</t>
         </is>
       </c>
     </row>

--- a/data/loto_pool.xlsx
+++ b/data/loto_pool.xlsx
@@ -9043,7 +9043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B270"/>
+  <dimension ref="A1:B271"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12278,6 +12278,18 @@
       <c r="B270" s="2" t="inlineStr">
         <is>
           <t>01, 16, 20, 24, 27</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15  Jue</t>
+        </is>
+      </c>
+      <c r="B271" s="2" t="inlineStr">
+        <is>
+          <t>05, 06, 09, 16, 24</t>
         </is>
       </c>
     </row>

--- a/data/loto_pool.xlsx
+++ b/data/loto_pool.xlsx
@@ -9043,7 +9043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B271"/>
+  <dimension ref="A1:B272"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12290,6 +12290,18 @@
       <c r="B271" s="2" t="inlineStr">
         <is>
           <t>05, 06, 09, 16, 24</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16  Vie</t>
+        </is>
+      </c>
+      <c r="B272" s="2" t="inlineStr">
+        <is>
+          <t>02, 10, 17, 23, 29</t>
         </is>
       </c>
     </row>

--- a/data/loto_pool.xlsx
+++ b/data/loto_pool.xlsx
@@ -9043,7 +9043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B272"/>
+  <dimension ref="A1:B273"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12302,6 +12302,18 @@
       <c r="B272" s="2" t="inlineStr">
         <is>
           <t>02, 10, 17, 23, 29</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-17  Sáb</t>
+        </is>
+      </c>
+      <c r="B273" s="2" t="inlineStr">
+        <is>
+          <t>02, 13, 15, 20, 30</t>
         </is>
       </c>
     </row>

--- a/data/loto_pool.xlsx
+++ b/data/loto_pool.xlsx
@@ -9043,7 +9043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B273"/>
+  <dimension ref="A1:B274"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12314,6 +12314,18 @@
       <c r="B273" s="2" t="inlineStr">
         <is>
           <t>02, 13, 15, 20, 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-18  Dom</t>
+        </is>
+      </c>
+      <c r="B274" s="2" t="inlineStr">
+        <is>
+          <t>02, 11, 15, 26, 28</t>
         </is>
       </c>
     </row>

--- a/data/loto_pool.xlsx
+++ b/data/loto_pool.xlsx
@@ -9043,7 +9043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B274"/>
+  <dimension ref="A1:B275"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12326,6 +12326,18 @@
       <c r="B274" s="2" t="inlineStr">
         <is>
           <t>02, 11, 15, 26, 28</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19  Lun</t>
+        </is>
+      </c>
+      <c r="B275" s="2" t="inlineStr">
+        <is>
+          <t>03, 18, 28, 29, 31</t>
         </is>
       </c>
     </row>

--- a/data/loto_pool.xlsx
+++ b/data/loto_pool.xlsx
@@ -9043,7 +9043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B275"/>
+  <dimension ref="A1:B276"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12338,6 +12338,18 @@
       <c r="B275" s="2" t="inlineStr">
         <is>
           <t>03, 18, 28, 29, 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20  Mar</t>
+        </is>
+      </c>
+      <c r="B276" s="2" t="inlineStr">
+        <is>
+          <t>16, 18, 19, 20, 30</t>
         </is>
       </c>
     </row>

--- a/data/loto_pool.xlsx
+++ b/data/loto_pool.xlsx
@@ -9043,7 +9043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B276"/>
+  <dimension ref="A1:B277"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12350,6 +12350,18 @@
       <c r="B276" s="2" t="inlineStr">
         <is>
           <t>16, 18, 19, 20, 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21  Mié</t>
+        </is>
+      </c>
+      <c r="B277" s="2" t="inlineStr">
+        <is>
+          <t>12, 16, 24, 30, 31</t>
         </is>
       </c>
     </row>

--- a/data/loto_pool.xlsx
+++ b/data/loto_pool.xlsx
@@ -9043,7 +9043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B277"/>
+  <dimension ref="A1:B278"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12362,6 +12362,18 @@
       <c r="B277" s="2" t="inlineStr">
         <is>
           <t>12, 16, 24, 30, 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22  Jue</t>
+        </is>
+      </c>
+      <c r="B278" s="2" t="inlineStr">
+        <is>
+          <t>02, 08, 09, 21, 23</t>
         </is>
       </c>
     </row>

--- a/data/loto_pool.xlsx
+++ b/data/loto_pool.xlsx
@@ -9043,7 +9043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B278"/>
+  <dimension ref="A1:B279"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12374,6 +12374,18 @@
       <c r="B278" s="2" t="inlineStr">
         <is>
           <t>02, 08, 09, 21, 23</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23  Vie</t>
+        </is>
+      </c>
+      <c r="B279" s="2" t="inlineStr">
+        <is>
+          <t>14, 16, 19, 28, 31</t>
         </is>
       </c>
     </row>

--- a/data/loto_pool.xlsx
+++ b/data/loto_pool.xlsx
@@ -9043,7 +9043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B279"/>
+  <dimension ref="A1:B280"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12386,6 +12386,18 @@
       <c r="B279" s="2" t="inlineStr">
         <is>
           <t>14, 16, 19, 28, 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24  Sáb</t>
+        </is>
+      </c>
+      <c r="B280" s="2" t="inlineStr">
+        <is>
+          <t>10, 12, 14, 21, 24</t>
         </is>
       </c>
     </row>

--- a/data/loto_pool.xlsx
+++ b/data/loto_pool.xlsx
@@ -9043,7 +9043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B280"/>
+  <dimension ref="A1:B281"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12398,6 +12398,18 @@
       <c r="B280" s="2" t="inlineStr">
         <is>
           <t>10, 12, 14, 21, 24</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25  Dom</t>
+        </is>
+      </c>
+      <c r="B281" s="2" t="inlineStr">
+        <is>
+          <t>03, 09, 16, 27, 29</t>
         </is>
       </c>
     </row>

--- a/data/loto_pool.xlsx
+++ b/data/loto_pool.xlsx
@@ -9043,7 +9043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B281"/>
+  <dimension ref="A1:B282"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12410,6 +12410,18 @@
       <c r="B281" s="2" t="inlineStr">
         <is>
           <t>03, 09, 16, 27, 29</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26  Lun</t>
+        </is>
+      </c>
+      <c r="B282" s="2" t="inlineStr">
+        <is>
+          <t>21, 22, 23, 26, 28</t>
         </is>
       </c>
     </row>

--- a/data/loto_pool.xlsx
+++ b/data/loto_pool.xlsx
@@ -9043,7 +9043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B282"/>
+  <dimension ref="A1:B283"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12422,6 +12422,18 @@
       <c r="B282" s="2" t="inlineStr">
         <is>
           <t>21, 22, 23, 26, 28</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27  Mar</t>
+        </is>
+      </c>
+      <c r="B283" s="2" t="inlineStr">
+        <is>
+          <t>03, 11, 16, 18, 20</t>
         </is>
       </c>
     </row>

--- a/data/loto_pool.xlsx
+++ b/data/loto_pool.xlsx
@@ -9043,7 +9043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B283"/>
+  <dimension ref="A1:B284"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12434,6 +12434,18 @@
       <c r="B283" s="2" t="inlineStr">
         <is>
           <t>03, 11, 16, 18, 20</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28  Mié</t>
+        </is>
+      </c>
+      <c r="B284" s="2" t="inlineStr">
+        <is>
+          <t>01, 13, 15, 20, 28</t>
         </is>
       </c>
     </row>

--- a/data/loto_pool.xlsx
+++ b/data/loto_pool.xlsx
@@ -9043,7 +9043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B284"/>
+  <dimension ref="A1:B285"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12446,6 +12446,18 @@
       <c r="B284" s="2" t="inlineStr">
         <is>
           <t>01, 13, 15, 20, 28</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29  Jue</t>
+        </is>
+      </c>
+      <c r="B285" s="2" t="inlineStr">
+        <is>
+          <t>02, 04, 11, 26, 29</t>
         </is>
       </c>
     </row>
